--- a/ADD-ARTEFACT-XDM/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T13:57:35+00:00</t>
+    <t>2026-07-07T20:41:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ADD-ARTEFACT-XDM/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/StructureDefinition-DocumentEntry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="185">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T20:41:51+00:00</t>
+    <t>2026-07-09T18:09:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,168 +269,172 @@
     <t>DocumentEntry.logicalId</t>
   </si>
   <si>
+    <t>Cette métadonnée représente un identifiant invariable pour toutes les versions de la fiche d'un document, à la différence de la métadonnée entryUUID qui a une valeur différente pour chaque version de la fiche</t>
+  </si>
+  <si>
+    <t>DocumentEntry.mimeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le type de contenu du document, défini par le standard MIME.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.availabilityStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette métadonnée représente la pertinence de la version de la fiche d'un document. </t>
+  </si>
+  <si>
+    <t>**Availability Status**</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS|20200424120000</t>
+  </si>
+  <si>
+    <t>Non applicable, cette métadonnée n'est pas soumise par le système initiateur. Le registre du système cible gère cette information et fournit sa valeur en réponse à une requête stockée.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.hash</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient le résultat du hachage du document déposé</t>
+  </si>
+  <si>
+    <t>DocumentEntry.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée correspond à la taille du document déposé.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.languageCode</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le code de la langue dans laquelle le document est rédigé.</t>
+  </si>
+  <si>
+    <t>Pour tous les documents produits système initiateur français : 'fr-FR'</t>
+  </si>
+  <si>
+    <t>DocumentEntry.author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/AuthorDocumentEntry
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente les personnes physiques et/ou les systèmes (dispositifs, automates, services numériques référencés…) auteurs d’un document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.legalAuthenticator[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPS
+https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPatienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorSystem</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l'acteur prenant la responsabilité du contenu médical du document</t>
+  </si>
+  <si>
+    <t>XCN</t>
+  </si>
+  <si>
+    <t>DocumentEntry.repositoryUniqueId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oid
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l'identifiant unique global de l'entrepôt de documents dans lequel est stocké le document</t>
+  </si>
+  <si>
+    <t>DocumentEntry.serviceStartTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente la date de début de l'acte de référence.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.serviceStopTime</t>
+  </si>
+  <si>
+    <t>Cette métadonnée correspond à la date de fin de l'acte de référence, si connue.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.sourcePatientID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientId
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient l'identifiant secondaire du patient dans le système d'information du producteur (IPP) ou l'INS, s'il n'y a pas d'identifiant secondaire.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.sourcePatientInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientInfo
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient les traits d'identité du patient concerné par le document, connus par le producteur du document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.URI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée n'est exploitée que par la transaction XDM 'Distribute document set on media ITI-32'</t>
+  </si>
+  <si>
+    <t>DocumentEntry.title</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le titre du document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.comments</t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient le commentaire associé au document.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.patientID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/PatientId
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient lorsque celui-ci est qualifié.</t>
+  </si>
+  <si>
+    <t>DocumentEntry.uniqueId</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identifier
 </t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente un identifiant invariable pour toutes les versions de la fiche d'un document, à la différence de la métadonnée entryUUID qui a une valeur différente pour chaque version de la fiche</t>
-  </si>
-  <si>
-    <t>DocumentEntry.mimeType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le type de contenu du document, défini par le standard MIME.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.availabilityStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cette métadonnée représente la pertinence de la version de la fiche d'un document. </t>
-  </si>
-  <si>
-    <t>**Availability Status**</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS|20200424120000</t>
-  </si>
-  <si>
-    <t>Non applicable, cette métadonnée n'est pas soumise par le système initiateur. Le registre du système cible gère cette information et fournit sa valeur en réponse à une requête stockée.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.hash</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient le résultat du hachage du document déposé</t>
-  </si>
-  <si>
-    <t>DocumentEntry.size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée correspond à la taille du document déposé.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.languageCode</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le code de la langue dans laquelle le document est rédigé.</t>
-  </si>
-  <si>
-    <t>Pour tous les documents produits système initiateur français : 'fr-FR'</t>
-  </si>
-  <si>
-    <t>DocumentEntry.author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/AuthorDocumentEntry
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente les personnes physiques et/ou les systèmes (dispositifs, automates, services numériques référencés…) auteurs d’un document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.legalAuthenticator[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPS
-https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorPatienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/ActorSystem</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente l'acteur prenant la responsabilité du contenu médical du document</t>
-  </si>
-  <si>
-    <t>XCN</t>
-  </si>
-  <si>
-    <t>DocumentEntry.repositoryUniqueId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oid
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente l'identifiant unique global de l'entrepôt de documents dans lequel est stocké le document</t>
-  </si>
-  <si>
-    <t>DocumentEntry.serviceStartTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente la date de début de l'acte de référence.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.serviceEndTime</t>
-  </si>
-  <si>
-    <t>Cette métadonnée correspond à la date de fin de l'acte de référence, si connue.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.sourcePatientID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientId
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient l'identifiant secondaire du patient dans le système d'information du producteur (IPP) ou l'INS, s'il n'y a pas d'identifiant secondaire.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.sourcePatientInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/SourcePatientInfo
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient les traits d'identité du patient concerné par le document, connus par le producteur du document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.URI</t>
-  </si>
-  <si>
-    <t>Cette métadonnée n'est exploitée que par la transaction XDM 'Distribute document set on media ITI-32'</t>
-  </si>
-  <si>
-    <t>DocumentEntry.title</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le titre du document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.comments</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient le commentaire associé au document.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.patientID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/PatientId
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient.</t>
-  </si>
-  <si>
-    <t>DocumentEntry.uniqueId</t>
   </si>
   <si>
     <t xml:space="preserve">Identifiant unique affecté au document par son créateur. </t>
@@ -596,12 +600,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS|20220624120000</t>
-  </si>
-  <si>
-    <t>DocumentEntry.version</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente le numéro de version de la fiche d’un document.</t>
   </si>
 </sst>
 </file>
@@ -903,7 +901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.6015625" customWidth="true" bestFit="true"/>
@@ -1291,13 +1289,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1368,10 +1366,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1394,13 +1392,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1451,7 +1449,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -1471,10 +1469,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1497,13 +1495,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1530,52 +1528,52 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1598,13 +1596,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1655,7 +1653,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
@@ -1675,10 +1673,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1701,13 +1699,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L8" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="M8" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1758,7 +1756,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -1778,10 +1776,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1804,13 +1802,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1861,7 +1859,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -1881,10 +1879,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1907,13 +1905,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1964,7 +1962,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -1984,10 +1982,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2010,13 +2008,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2067,7 +2065,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2087,10 +2085,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2113,13 +2111,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2170,7 +2168,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2190,10 +2188,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2216,13 +2214,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2273,7 +2271,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2293,10 +2291,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2319,13 +2317,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2376,7 +2374,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2396,10 +2394,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2422,13 +2420,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2479,7 +2477,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2499,10 +2497,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2525,13 +2523,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>124</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2582,7 +2580,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2602,10 +2600,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2628,7 +2626,7 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>126</v>
@@ -2685,7 +2683,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2731,7 +2729,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>128</v>
@@ -2834,7 +2832,7 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>130</v>
@@ -3040,13 +3038,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3117,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3143,13 +3141,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3176,11 +3174,11 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3198,7 +3196,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3213,15 +3211,15 @@
         <v>73</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3232,7 +3230,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3244,13 +3242,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3277,11 +3275,11 @@
         <v>73</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3299,13 +3297,13 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
@@ -3319,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3345,13 +3343,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3402,7 +3400,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3422,10 +3420,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3448,13 +3446,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3481,11 +3479,11 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3503,7 +3501,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3523,10 +3521,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3549,13 +3547,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3582,11 +3580,11 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3604,7 +3602,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3624,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3650,13 +3648,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3683,11 +3681,11 @@
         <v>73</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3705,7 +3703,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -3725,10 +3723,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3751,13 +3749,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3784,11 +3782,11 @@
         <v>73</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>73</v>
@@ -3806,7 +3804,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3826,10 +3824,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3852,13 +3850,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3909,7 +3907,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3929,10 +3927,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3955,13 +3953,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4012,7 +4010,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4032,10 +4030,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4058,13 +4056,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4115,7 +4113,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4135,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4161,13 +4159,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4218,7 +4216,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4238,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4264,13 +4262,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4321,7 +4319,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4341,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4367,13 +4365,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4424,7 +4422,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4444,10 +4442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4470,13 +4468,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4503,11 +4501,11 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>73</v>
@@ -4525,7 +4523,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4540,109 +4538,6 @@
         <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK36" t="s" s="2">
         <v>73</v>
       </c>
     </row>
